--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.74186903842715</v>
+        <v>5.808053718744413</v>
       </c>
       <c r="D2" t="n">
-        <v>35.90475829271639</v>
+        <v>5.834523222566413</v>
       </c>
       <c r="E2" t="n">
-        <v>16.48108052178705</v>
+        <v>2.678175584790396</v>
       </c>
       <c r="F2" t="n">
-        <v>16.1390141800753</v>
+        <v>2.622589804262236</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.50858473910841</v>
+        <v>7.882645020105117</v>
       </c>
       <c r="D3" t="n">
-        <v>48.32905858860056</v>
+        <v>7.853472020647591</v>
       </c>
       <c r="E3" t="n">
-        <v>16.48108052178705</v>
+        <v>2.678175584790396</v>
       </c>
       <c r="F3" t="n">
-        <v>16.1390141800753</v>
+        <v>2.622589804262236</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>73.78295586342726</v>
+        <v>11.98973032780693</v>
       </c>
       <c r="D4" t="n">
-        <v>74.96795433935132</v>
+        <v>12.18229258014459</v>
       </c>
       <c r="E4" t="n">
-        <v>16.48108052178705</v>
+        <v>2.678175584790396</v>
       </c>
       <c r="F4" t="n">
-        <v>16.1390141800753</v>
+        <v>2.622589804262236</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>73.49583159384889</v>
+        <v>11.94307263400045</v>
       </c>
       <c r="D5" t="n">
-        <v>74.34332602682517</v>
+        <v>12.08079047935909</v>
       </c>
       <c r="E5" t="n">
-        <v>16.48108052178705</v>
+        <v>2.678175584790396</v>
       </c>
       <c r="F5" t="n">
-        <v>16.1390141800753</v>
+        <v>2.622589804262236</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.05906573075952</v>
+        <v>6.347098181248422</v>
       </c>
       <c r="D6" t="n">
-        <v>43.97303686621282</v>
+        <v>7.145618490759583</v>
       </c>
       <c r="E6" t="n">
-        <v>16.48108052178705</v>
+        <v>2.678175584790396</v>
       </c>
       <c r="F6" t="n">
-        <v>16.1390141800753</v>
+        <v>2.622589804262236</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
